--- a/validation/expert_reviews/E6_extraction_review.xlsx
+++ b/validation/expert_reviews/E6_extraction_review.xlsx
@@ -580,7 +580,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Review workbook — Peter</t>
+          <t>Review workbook — E6</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E6    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Peter</t>
+          <t>Rating — E6</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E6    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Peter</t>
+          <t>Rating — E6</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E6    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Peter</t>
+          <t>Rating — E6</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E6    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Peter</t>
+          <t>Rating — E6</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E6    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Peter</t>
+          <t>Rating — E6</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E6    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Peter</t>
+          <t>Rating — E6</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E6    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4327,6 +4327,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4442,6 +4443,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -4784,7 +4786,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E6    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4844,6 +4846,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4959,6 +4962,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5301,7 +5305,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E6    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5361,6 +5365,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5476,6 +5481,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5818,7 +5824,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E6    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5878,6 +5884,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5993,6 +6000,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6335,7 +6343,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E6    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6395,6 +6403,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -6510,6 +6519,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6852,7 +6862,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E6    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6912,6 +6922,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -7027,6 +7038,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -7369,7 +7381,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E6    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -7429,6 +7441,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -7544,6 +7557,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -7891,7 +7905,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Peter    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E6    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7924,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Peter</t>
+          <t>Rating — E6</t>
         </is>
       </c>
     </row>
